--- a/data/examples/demo_data.xlsx
+++ b/data/examples/demo_data.xlsx
@@ -9,7 +9,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="74">
   <si>
     <t>Employee Directory - Sheet 1</t>
   </si>
@@ -35,7 +35,7 @@
     <t>Software Engineer</t>
   </si>
   <si>
-    <t>2022-01-15</t>
+    <t>2021-03-15</t>
   </si>
   <si>
     <t>Bob Williams</t>
@@ -44,97 +44,193 @@
     <t>Marketing</t>
   </si>
   <si>
-    <t>Marketing Manager</t>
-  </si>
-  <si>
-    <t>2021-06-01</t>
-  </si>
-  <si>
-    <t>Carol Davis</t>
+    <t>Marketing Specialist</t>
+  </si>
+  <si>
+    <t>2020-07-01</t>
+  </si>
+  <si>
+    <t>Charlie Brown</t>
+  </si>
+  <si>
+    <t>Human Resources</t>
+  </si>
+  <si>
+    <t>HR Manager</t>
+  </si>
+  <si>
+    <t>2019-11-20</t>
+  </si>
+  <si>
+    <t>Diana Prince</t>
   </si>
   <si>
     <t>Sales</t>
   </si>
   <si>
-    <t>Account Executive</t>
-  </si>
-  <si>
-    <t>2023-03-10</t>
-  </si>
-  <si>
-    <t>David Brown</t>
+    <t>Account Manager</t>
+  </si>
+  <si>
+    <t>2022-01-10</t>
+  </si>
+  <si>
+    <t>Eve Adams</t>
+  </si>
+  <si>
+    <t>Finance</t>
+  </si>
+  <si>
+    <t>Financial Analyst</t>
+  </si>
+  <si>
+    <t>2021-09-01</t>
+  </si>
+  <si>
+    <t>Frank Miller</t>
+  </si>
+  <si>
+    <t>Operations</t>
+  </si>
+  <si>
+    <t>Operations Coordinator</t>
+  </si>
+  <si>
+    <t>2023-02-28</t>
+  </si>
+  <si>
+    <t>Grace Kelly</t>
+  </si>
+  <si>
+    <t>IT</t>
+  </si>
+  <si>
+    <t>Network Administrator</t>
+  </si>
+  <si>
+    <t>2020-05-15</t>
+  </si>
+  <si>
+    <t>Henry Davis</t>
+  </si>
+  <si>
+    <t>Engineering</t>
+  </si>
+  <si>
+    <t>Senior Software Engineer</t>
+  </si>
+  <si>
+    <t>2018-04-01</t>
+  </si>
+  <si>
+    <t>Employee Directory - Sheet 2</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Department</t>
+  </si>
+  <si>
+    <t>Role</t>
+  </si>
+  <si>
+    <t>Start Date</t>
+  </si>
+  <si>
+    <t>Isabel Garcia</t>
+  </si>
+  <si>
+    <t>Marketing</t>
+  </si>
+  <si>
+    <t>Marketing Director</t>
+  </si>
+  <si>
+    <t>2017-08-01</t>
+  </si>
+  <si>
+    <t>Jack Robinson</t>
+  </si>
+  <si>
+    <t>Sales</t>
+  </si>
+  <si>
+    <t>Sales Representative</t>
+  </si>
+  <si>
+    <t>2023-01-15</t>
+  </si>
+  <si>
+    <t>Karen White</t>
   </si>
   <si>
     <t>Human Resources</t>
   </si>
   <si>
-    <t>HR Specialist</t>
-  </si>
-  <si>
-    <t>2022-11-01</t>
-  </si>
-  <si>
-    <t>Employee Directory - Sheet 2</t>
-  </si>
-  <si>
-    <t>Name</t>
-  </si>
-  <si>
-    <t>Department</t>
-  </si>
-  <si>
-    <t>Role</t>
-  </si>
-  <si>
-    <t>Start Date</t>
-  </si>
-  <si>
-    <t>Eve Miller</t>
+    <t>Recruitment Specialist</t>
+  </si>
+  <si>
+    <t>2022-06-01</t>
+  </si>
+  <si>
+    <t>Liam Hall</t>
+  </si>
+  <si>
+    <t>Finance</t>
+  </si>
+  <si>
+    <t>Chief Financial Officer</t>
+  </si>
+  <si>
+    <t>2015-02-01</t>
+  </si>
+  <si>
+    <t>Mia King</t>
   </si>
   <si>
     <t>Engineering</t>
   </si>
   <si>
-    <t>QA Tester</t>
-  </si>
-  <si>
-    <t>2023-01-20</t>
-  </si>
-  <si>
-    <t>Frank White</t>
-  </si>
-  <si>
-    <t>Finance</t>
-  </si>
-  <si>
-    <t>Financial Analyst</t>
-  </si>
-  <si>
-    <t>2021-09-15</t>
-  </si>
-  <si>
-    <t>Grace Lee</t>
+    <t>QA Engineer</t>
+  </si>
+  <si>
+    <t>2022-10-01</t>
+  </si>
+  <si>
+    <t>Noah Lee</t>
+  </si>
+  <si>
+    <t>IT</t>
+  </si>
+  <si>
+    <t>IT Support Specialist</t>
+  </si>
+  <si>
+    <t>2023-03-20</t>
+  </si>
+  <si>
+    <t>Olivia Scott</t>
+  </si>
+  <si>
+    <t>Operations</t>
+  </si>
+  <si>
+    <t>Logistics Manager</t>
+  </si>
+  <si>
+    <t>2021-04-10</t>
+  </si>
+  <si>
+    <t>Peter Green</t>
   </si>
   <si>
     <t>Marketing</t>
   </si>
   <si>
-    <t>Social Media Coordinator</t>
-  </si>
-  <si>
-    <t>2023-04-01</t>
-  </si>
-  <si>
-    <t>Henry Green</t>
-  </si>
-  <si>
-    <t>Sales</t>
-  </si>
-  <si>
-    <t>Sales Director</t>
-  </si>
-  <si>
-    <t>2020-07-01</t>
+    <t>Content Creator</t>
+  </si>
+  <si>
+    <t>2022-11-05</t>
   </si>
 </sst>
 </file>
@@ -254,6 +350,62 @@
         <v>20</v>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>25</v>
+      </c>
+      <c r="B8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C8" t="s">
+        <v>27</v>
+      </c>
+      <c r="D8" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>29</v>
+      </c>
+      <c r="B9" t="s">
+        <v>30</v>
+      </c>
+      <c r="C9" t="s">
+        <v>31</v>
+      </c>
+      <c r="D9" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>33</v>
+      </c>
+      <c r="B10" t="s">
+        <v>6</v>
+      </c>
+      <c r="C10" t="s">
+        <v>35</v>
+      </c>
+      <c r="D10" t="s">
+        <v>36</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
@@ -263,7 +415,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>21</v>
+        <v>37</v>
       </c>
     </row>
     <row r="2">
@@ -282,58 +434,114 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="B3" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C3" t="s">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="D3" t="s">
-        <v>29</v>
+        <v>45</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="B4" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="C4" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="D4" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="B5" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="D5" t="s">
-        <v>37</v>
+        <v>53</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="B6" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="C6" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="D6" t="s">
-        <v>41</v>
+        <v>57</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>58</v>
+      </c>
+      <c r="B7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" t="s">
+        <v>60</v>
+      </c>
+      <c r="D7" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>62</v>
+      </c>
+      <c r="B8" t="s">
+        <v>30</v>
+      </c>
+      <c r="C8" t="s">
+        <v>64</v>
+      </c>
+      <c r="D8" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>66</v>
+      </c>
+      <c r="B9" t="s">
+        <v>26</v>
+      </c>
+      <c r="C9" t="s">
+        <v>68</v>
+      </c>
+      <c r="D9" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>70</v>
+      </c>
+      <c r="B10" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10" t="s">
+        <v>72</v>
+      </c>
+      <c r="D10" t="s">
+        <v>73</v>
       </c>
     </row>
   </sheetData>
